--- a/agent_runs/manjidiwang/episodes/ep08/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep08/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>班委竞选（，总时长：10秒，镜头数：4个）</t>
+          <t>班委竞选</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>生活委员之辱（，总时长：10秒，镜头数：4个）</t>
+          <t>生活委员之辱</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>督察长之议（，总时长：10秒，镜头数：5个）</t>
+          <t>督察长之议</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>权力倾斜（，总时长：10秒，镜头数：4个）</t>
+          <t>权力倾斜</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>名正言顺（，总时长：12秒，镜头数：5个）</t>
+          <t>名正言顺</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>天台密谋（，总时长：10秒，镜头数：5个）</t>
+          <t>天台密谋</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>偷题计划（，总时长：10秒，镜头数：5个）</t>
+          <t>偷题计划</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>监控反制（，总时长：14秒，镜头数：6个）</t>
+          <t>监控反制</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>赢得体面（，总时长：11秒，镜头数：4个）</t>
+          <t>赢得体面</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
